--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -4127,7 +4127,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118734631</v>
+        <v>118734628</v>
       </c>
       <c r="B29" t="n">
         <v>97846</v>
@@ -4162,12 +4162,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4183,17 +4183,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekudden knärot 550 m n, Srm</t>
+          <t>Ekudden (knärot) 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575114</v>
+        <v>575082</v>
       </c>
       <c r="R29" t="n">
-        <v>6536053</v>
+        <v>6536091</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>D-Kat-0553</t>
+          <t>D-Kat-0194</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4394,10 +4394,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118734643</v>
+        <v>118734631</v>
       </c>
       <c r="B31" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4406,45 +4406,61 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekudden 600 m n, Srm</t>
+          <t>Ekudden knärot 550 m n, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575082</v>
+        <v>575114</v>
       </c>
       <c r="R31" t="n">
-        <v>6536091</v>
+        <v>6536053</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4464,6 +4480,11 @@
       <c r="W31" t="inlineStr">
         <is>
           <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D-Kat-0553</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4507,14 +4528,18 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118734628</v>
+        <v>118734643</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4523,51 +4548,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekudden (knärot) 600 m n, Srm</t>
+          <t>Ekudden 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4599,11 +4608,6 @@
           <t>Stora Malm</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>D-Kat-0194</t>
-        </is>
-      </c>
       <c r="Y32" t="inlineStr">
         <is>
           <t>2024-07-22</t>
@@ -4645,11 +4649,7 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -4127,10 +4127,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118734628</v>
+        <v>118734641</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>96808</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4139,30 +4139,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>224358</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4170,11 +4166,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
@@ -4183,7 +4175,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekudden (knärot) 600 m n, Srm</t>
+          <t>Ekudden 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -4215,11 +4207,6 @@
           <t>Stora Malm</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>D-Kat-0194</t>
-        </is>
-      </c>
       <c r="Y29" t="inlineStr">
         <is>
           <t>2024-07-22</t>
@@ -4261,18 +4248,14 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118734641</v>
+        <v>118734628</v>
       </c>
       <c r="B30" t="n">
-        <v>96808</v>
+        <v>97846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,26 +4264,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>224358</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4308,7 +4295,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
@@ -4317,7 +4308,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekudden 600 m n, Srm</t>
+          <t>Ekudden (knärot) 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -4349,6 +4340,11 @@
           <t>Stora Malm</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D-Kat-0194</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>2024-07-22</t>
@@ -4390,14 +4386,18 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118734631</v>
+        <v>118734643</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4406,61 +4406,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekudden knärot 550 m n, Srm</t>
+          <t>Ekudden 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575114</v>
+        <v>575082</v>
       </c>
       <c r="R31" t="n">
-        <v>6536053</v>
+        <v>6536091</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4480,11 +4464,6 @@
       <c r="W31" t="inlineStr">
         <is>
           <t>Stora Malm</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>D-Kat-0553</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4528,18 +4507,14 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118734643</v>
+        <v>118734631</v>
       </c>
       <c r="B32" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4548,45 +4523,61 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekudden 600 m n, Srm</t>
+          <t>Ekudden knärot 550 m n, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575082</v>
+        <v>575114</v>
       </c>
       <c r="R32" t="n">
-        <v>6536091</v>
+        <v>6536053</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4606,6 +4597,11 @@
       <c r="W32" t="inlineStr">
         <is>
           <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D-Kat-0553</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4649,7 +4645,11 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -4127,10 +4127,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118734641</v>
+        <v>118734643</v>
       </c>
       <c r="B29" t="n">
-        <v>96808</v>
+        <v>104947</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4143,36 +4143,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>224358</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ekudden 600 m n, Srm</t>
@@ -4255,7 +4247,7 @@
         <v>118734628</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4394,10 +4386,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118734643</v>
+        <v>118734631</v>
       </c>
       <c r="B31" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4406,45 +4398,61 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekudden 600 m n, Srm</t>
+          <t>Ekudden knärot 550 m n, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575082</v>
+        <v>575114</v>
       </c>
       <c r="R31" t="n">
-        <v>6536091</v>
+        <v>6536053</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4464,6 +4472,11 @@
       <c r="W31" t="inlineStr">
         <is>
           <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D-Kat-0553</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4507,14 +4520,18 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118734631</v>
+        <v>118734641</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>96815</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4523,42 +4540,34 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>224358</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
@@ -4567,17 +4576,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekudden knärot 550 m n, Srm</t>
+          <t>Ekudden 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575114</v>
+        <v>575082</v>
       </c>
       <c r="R32" t="n">
-        <v>6536053</v>
+        <v>6536091</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4597,11 +4606,6 @@
       <c r="W32" t="inlineStr">
         <is>
           <t>Stora Malm</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>D-Kat-0553</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4645,11 +4649,7 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -4127,10 +4127,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118734643</v>
+        <v>118734628</v>
       </c>
       <c r="B29" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4139,35 +4139,51 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekudden 600 m n, Srm</t>
+          <t>Ekudden (knärot) 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -4199,6 +4215,11 @@
           <t>Stora Malm</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D-Kat-0194</t>
+        </is>
+      </c>
       <c r="Y29" t="inlineStr">
         <is>
           <t>2024-07-22</t>
@@ -4240,14 +4261,18 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118734628</v>
+        <v>118734643</v>
       </c>
       <c r="B30" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4256,51 +4281,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekudden (knärot) 600 m n, Srm</t>
+          <t>Ekudden 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -4332,11 +4341,6 @@
           <t>Stora Malm</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>D-Kat-0194</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>2024-07-22</t>
@@ -4378,11 +4382,7 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4127,10 +4127,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118734631</v>
+        <v>118734641</v>
       </c>
       <c r="B29" t="n">
-        <v>97858</v>
+        <v>96820</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4139,42 +4139,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>224358</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
@@ -4183,17 +4175,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekudden knärot 550 m n, Srm</t>
+          <t>Ekudden 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575114</v>
+        <v>575082</v>
       </c>
       <c r="R29" t="n">
-        <v>6536053</v>
+        <v>6536091</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4213,11 +4205,6 @@
       <c r="W29" t="inlineStr">
         <is>
           <t>Stora Malm</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>D-Kat-0553</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4261,18 +4248,14 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118734641</v>
+        <v>118734643</v>
       </c>
       <c r="B30" t="n">
-        <v>96820</v>
+        <v>104952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4285,36 +4268,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>224358</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ekudden 600 m n, Srm</t>
@@ -4391,265 +4366,6 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>118734643</v>
-      </c>
-      <c r="B31" t="n">
-        <v>104952</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Ekudden 600 m n, Srm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>575082</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6536091</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Stora Malm</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>118734628</v>
-      </c>
-      <c r="B32" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Ekudden (knärot) 600 m n, Srm</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>575082</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6536091</v>
-      </c>
-      <c r="S32" t="n">
-        <v>25</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Stora Malm</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>D-Kat-0194</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6219924</v>
+        <v>67544704</v>
       </c>
       <c r="B2" t="n">
-        <v>95520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>972</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosentrattskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Pseudoclitopilus rhodoleucus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Sacc.) Vizzini &amp; Contu</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ekudden 650 m n, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575011.6266864444</v>
+        <v>575012</v>
       </c>
       <c r="R2" t="n">
-        <v>6536030.612718226</v>
+        <v>6536031</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -750,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-02-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-02-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +756,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog</t>
+          <t>Barrbladskog,</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,16 +788,11 @@
         <v>399064</v>
       </c>
       <c r="B3" t="n">
-        <v>81971</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -846,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575011.6266864444</v>
+        <v>575012</v>
       </c>
       <c r="R3" t="n">
-        <v>6536030.612718226</v>
+        <v>6536031</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +862,9 @@
           <t>2008-02-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-02-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,58 +896,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6229492</v>
+        <v>7177003</v>
       </c>
       <c r="B4" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224364</v>
+        <v>1445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ekudden 650 m n, Srm</t>
+          <t>Ekudden 675 m n, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575011.6266864444</v>
+        <v>574967</v>
       </c>
       <c r="R4" t="n">
-        <v>6536030.612718226</v>
+        <v>6536034</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2008-02-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-02-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2008-02-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-02-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,12 +985,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>MARKSLAG</t>
+        </is>
+      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog</t>
+          <t>Grandominerad skog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,56 +1014,58 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7027720</v>
+        <v>17191292</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>1445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ekudden 650 m n, Srm</t>
+          <t>Ekudden 650 m no, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575011.6266864444</v>
+        <v>574982</v>
       </c>
       <c r="R5" t="n">
-        <v>6536030.612718226</v>
+        <v>6536020</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,22 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,8 +1103,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>MARKSLAG</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Grandominerad blandskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1160,64 +1132,58 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7177027</v>
+        <v>17191295</v>
       </c>
       <c r="B6" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>1445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ekudden 625 m n, Srm</t>
+          <t>Ekudden 650 m no, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575092.6639003595</v>
+        <v>574986</v>
       </c>
       <c r="R6" t="n">
-        <v>6536115.777288955</v>
+        <v>6536005</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,22 +1207,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,17 +1221,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>MARKSLAG</t>
-        </is>
-      </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Grandominerad blandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1293,64 +1245,58 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7177032</v>
+        <v>17191296</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ekudden 600 m n, Srm</t>
+          <t>Ekudden 650 m no, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575081.7704466349</v>
+        <v>574982</v>
       </c>
       <c r="R7" t="n">
-        <v>6536091.315354088</v>
+        <v>6536052</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,27 +1320,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 lokaler 28+12 skott</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,8 +1334,14 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grandominerad blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1421,19 +1358,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7177003</v>
+        <v>57804598</v>
       </c>
       <c r="B8" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1456,7 +1388,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1467,17 +1399,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ekudden 675 m n, Srm</t>
+          <t>Ekudden 640 m no, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574966.5851426019</v>
+        <v>574958</v>
       </c>
       <c r="R8" t="n">
-        <v>6536034.378041334</v>
+        <v>6535980</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,22 +1433,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,12 +1453,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>MARKSLAG</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad skog</t>
+          <t>Grandominerad barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1554,64 +1476,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16709111</v>
+        <v>91878510</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karlsro 350 m nv, Srm</t>
+          <t>Forssjö 370 m no, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575155.1827484618</v>
+        <v>575000</v>
       </c>
       <c r="R9" t="n">
-        <v>6536037.542932893</v>
+        <v>6536055</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,22 +1552,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-10-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-10-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ny plats</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,17 +1571,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Sandbarrskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Talldominerad Barrblandskog</t>
+          <t>Grandominerad barrblandskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1687,55 +1600,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16837812</v>
+        <v>92289603</v>
       </c>
       <c r="B10" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ekudden 650 m n, Srm</t>
+          <t>Forssjöskogen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575011.6266864444</v>
+        <v>574997</v>
       </c>
       <c r="R10" t="n">
-        <v>6536030.612718226</v>
+        <v>6536025</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,22 +1675,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-11-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-11-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,38 +1689,36 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17191292</v>
+        <v>92289669</v>
       </c>
       <c r="B11" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1835,30 +1739,21 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ekudden 650 m no, Srm</t>
+          <t>Forssjöskogen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574981.85036159</v>
+        <v>575001</v>
       </c>
       <c r="R11" t="n">
-        <v>6536020.228999851</v>
+        <v>6536051</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1882,22 +1777,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,92 +1791,73 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>MARKSLAG</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grandominerad blandskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17191296</v>
+        <v>7027720</v>
       </c>
       <c r="B12" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1445</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ekudden 650 m no, Srm</t>
+          <t>Ekudden 650 m n, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574982.2602861294</v>
+        <v>575012</v>
       </c>
       <c r="R12" t="n">
-        <v>6536052.225879623</v>
+        <v>6536031</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2015,22 +1881,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,14 +1895,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad blandskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2063,63 +1913,51 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17191295</v>
+        <v>57804777</v>
       </c>
       <c r="B13" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ekudden 650 m no, Srm</t>
+          <t>Ekudden 640 m no, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574985.7587414775</v>
+        <v>574958</v>
       </c>
       <c r="R13" t="n">
-        <v>6536005.342565036</v>
+        <v>6535980</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2143,22 +1981,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2167,13 +1995,17 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad blandskog</t>
+          <t>Grandominerad barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2191,37 +2023,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67544704</v>
+        <v>16837812</v>
       </c>
       <c r="B14" t="n">
-        <v>88404</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>972</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosentrattskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudoclitopilus rhodoleucus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Vizzini &amp; Contu</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2233,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575011.6266864444</v>
+        <v>575012</v>
       </c>
       <c r="R14" t="n">
-        <v>6536030.612718226</v>
+        <v>6536031</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2263,22 +2090,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2290,16 +2107,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrbladskog,</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2319,16 +2126,11 @@
         <v>68865304</v>
       </c>
       <c r="B15" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2341,12 +2143,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2358,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575011.6266864444</v>
+        <v>575012</v>
       </c>
       <c r="R15" t="n">
-        <v>6536030.612718226</v>
+        <v>6536031</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2391,19 +2193,9 @@
           <t>2018-01-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2018-01-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2441,60 +2233,58 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68865315</v>
+        <v>109000844</v>
       </c>
       <c r="B16" t="n">
-        <v>95526</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224358</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ekudden 650 m n, Srm</t>
+          <t>Ändbäckkärret, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575011.6266864444</v>
+        <v>575068</v>
       </c>
       <c r="R16" t="n">
-        <v>6536030.612718226</v>
+        <v>6536075</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2518,22 +2308,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-01-02</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-01-02</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökte på död gran i avverkningsanmält område</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2544,41 +2339,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Grandominerad blandskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67782933</v>
+        <v>7177032</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2385,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2613,22 +2393,18 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ekudden (Knärot) 500 m n, Srm</t>
+          <t>Ekudden 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575162.0709143769</v>
+        <v>575082</v>
       </c>
       <c r="R17" t="n">
-        <v>6536028.906371513</v>
+        <v>6536091</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2653,29 +2429,19 @@
           <t>Stora Malm</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>D-Kat-0432</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-09-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-02-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-09-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-02-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 lokaler 28+12 skott</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2686,16 +2452,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2708,69 +2464,63 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>76809995</v>
+        <v>16709111</v>
       </c>
       <c r="B18" t="n">
-        <v>95526</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224358</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Forssjö no, Srm</t>
+          <t>Karlsro 350 m nv, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575111.1400976054</v>
+        <v>575155</v>
       </c>
       <c r="R18" t="n">
-        <v>6536096.01638487</v>
+        <v>6536038</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2794,22 +2544,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2818,18 +2558,17 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sandbarrskog</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>Talldominerad Barrblandskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2847,15 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>91878992</v>
+        <v>67782933</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2882,7 +2616,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2892,28 +2626,23 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekudden knärot 550 m n, Srm</t>
+          <t>Ekudden (Knärot) 500 m n, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575114.0529128641</v>
+        <v>575162</v>
       </c>
       <c r="R19" t="n">
-        <v>6536052.733850819</v>
+        <v>6536029</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2937,32 +2666,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>D-Kat-0553</t>
+          <t>D-Kat-0432</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2 dellokaler 13+3 ex</t>
+          <t>2017-09-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2971,7 +2685,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3004,15 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>91878510</v>
+        <v>91510073</v>
       </c>
       <c r="B20" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3020,48 +2728,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Forssjö 370 m no, Srm</t>
+          <t>Ändbäckkärret, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574999.7769785739</v>
+        <v>575068</v>
       </c>
       <c r="R20" t="n">
-        <v>6536055.14717287</v>
+        <v>6536075</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3085,27 +2784,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ny plats</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3114,44 +2798,32 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Grandominerad barrblandskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>92289669</v>
+        <v>91878992</v>
       </c>
       <c r="B21" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3159,38 +2831,57 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Forssjöskogen, Srm</t>
+          <t>Ekudden knärot 550 m n, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575000.8907927673</v>
+        <v>575114</v>
       </c>
       <c r="R21" t="n">
-        <v>6536051.041312378</v>
+        <v>6536053</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3212,24 +2903,24 @@
           <t>Stora Malm</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D-Kat-0553</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 dellokaler 13+3 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3238,37 +2929,43 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Lst D inventering sandbarrskogar</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>92289603</v>
+        <v>109002285</v>
       </c>
       <c r="B22" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3276,44 +2973,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Forssjöskogen, Srm</t>
+          <t>Ändbäckkärret, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574996.7435720876</v>
+        <v>575083</v>
       </c>
       <c r="R22" t="n">
-        <v>6536025.162955576</v>
+        <v>6536048</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3340,22 +3032,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3378,23 +3070,14 @@
           <t>Fredrik Enoksson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>91510073</v>
+        <v>109002581</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,19 +3102,27 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ändbäckkärret, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575068.1424767512</v>
+        <v>575109</v>
       </c>
       <c r="R23" t="n">
-        <v>6536074.539111541</v>
+        <v>6536069</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3458,22 +3149,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst, flera smågrupper inom avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3496,23 +3192,14 @@
           <t>Fredrik Enoksson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>99489779</v>
       </c>
       <c r="B24" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3560,10 +3247,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575011.6266864444</v>
+        <v>575012</v>
       </c>
       <c r="R24" t="n">
-        <v>6536030.612718226</v>
+        <v>6536031</v>
       </c>
       <c r="S24" t="n">
         <v>100</v>
@@ -3593,19 +3280,9 @@
           <t>2022-03-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-03-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3643,55 +3320,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109002285</v>
+        <v>118734643</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ändbäckkärret, Srm</t>
+          <t>Ekudden 600 m n, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575082.1096188766</v>
+        <v>575082</v>
       </c>
       <c r="R25" t="n">
-        <v>6536047.466566495</v>
+        <v>6536091</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3718,22 +3389,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3742,81 +3403,88 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109002581</v>
+        <v>7177027</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ändbäckkärret, Srm</t>
+          <t>Ekudden 625 m n, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575109.0905836107</v>
+        <v>575093</v>
       </c>
       <c r="R26" t="n">
-        <v>6536068.631302664</v>
+        <v>6536116</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3840,27 +3508,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:12</t>
+          <t>2014-02-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst, flera smågrupper inom avverkningsanmäld skog</t>
+          <t>2014-02-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3871,16 +3524,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>MARKSLAG</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3890,12 +3553,7 @@
         <v>109002923</v>
       </c>
       <c r="B27" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3928,10 +3586,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575096.4215633231</v>
+        <v>575097</v>
       </c>
       <c r="R27" t="n">
-        <v>6536108.627496871</v>
+        <v>6536109</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3961,19 +3619,9 @@
           <t>2023-05-12</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4000,63 +3648,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109000844</v>
+        <v>68865315</v>
       </c>
       <c r="B28" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97990</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100048</v>
+        <v>224358</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ändbäckkärret, Srm</t>
+          <t>Ekudden 650 m n, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575068.1424767512</v>
+        <v>575012</v>
       </c>
       <c r="R28" t="n">
-        <v>6536074.539111541</v>
+        <v>6536031</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4080,27 +3720,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:43</t>
+          <t>2018-01-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Födosökte på död gran i avverkningsanmält område</t>
+          <t>2018-01-02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4111,31 +3736,36 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Grandominerad blandskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118734641</v>
+        <v>76809995</v>
       </c>
       <c r="B29" t="n">
-        <v>96820</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97990</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4158,31 +3788,27 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekudden 600 m n, Srm</t>
+          <t>Forssjö no, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575082</v>
+        <v>575111</v>
       </c>
       <c r="R29" t="n">
-        <v>6536091</v>
+        <v>6536096</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4209,12 +3835,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4252,15 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118734643</v>
+        <v>118734641</v>
       </c>
       <c r="B30" t="n">
-        <v>104952</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97990</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4268,28 +3889,36 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>224358</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ekudden 600 m n, Srm</t>
@@ -4366,6 +3995,220 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6219924</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ekudden 650 m n, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>575012</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6536031</v>
+      </c>
+      <c r="S31" t="n">
+        <v>100</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2008-02-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2008-02-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6229492</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ekudden 650 m n, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>575012</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6536031</v>
+      </c>
+      <c r="S32" t="n">
+        <v>100</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2008-02-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2008-02-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67544704</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/399064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7177003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17191292</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17191295</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17191296</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57804598</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1597,6 +1637,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91878510</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1708,6 +1753,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92289603</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1808,6 +1858,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92289669</t>
         </is>
       </c>
     </row>
@@ -1910,6 +1965,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7027720</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2020,6 +2080,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57804777</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2120,6 +2185,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16837812</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68865304</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2352,6 +2427,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109000844</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2465,6 +2545,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7177032</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2583,6 +2668,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16709111</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2714,6 +2804,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67782933</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2817,6 +2912,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91510073</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2959,6 +3059,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91878992</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3071,6 +3176,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109002285</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3193,6 +3303,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109002581</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3317,6 +3432,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99489779</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3429,6 +3549,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118734643</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3547,6 +3672,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7177027</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3645,6 +3775,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109002923</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3759,6 +3894,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68865315</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3875,6 +4015,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76809995</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3995,6 +4140,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118734641</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4102,6 +4252,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6219924</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4209,8 +4364,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6229492</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>92289603</v>
       </c>
       <c r="B10" t="n">
-        <v>84158</v>
+        <v>84288</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>92289603</v>
       </c>
       <c r="B10" t="n">
-        <v>84288</v>
+        <v>84292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>92289603</v>
       </c>
       <c r="B10" t="n">
-        <v>84292</v>
+        <v>84298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>92289603</v>
       </c>
       <c r="B10" t="n">
-        <v>84298</v>
+        <v>84311</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>92289603</v>
       </c>
       <c r="B10" t="n">
-        <v>84311</v>
+        <v>84312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
